--- a/E/EG0A.xlsx
+++ b/E/EG0A.xlsx
@@ -61,7 +61,7 @@
     <t>20034077</t>
   </si>
   <si>
-    <t>F/F FULL CRM TPK 225</t>
+    <t>F/FLAG FCM TP 225 ML</t>
   </si>
   <si>
     <t>5</t>

--- a/E/EG0A.xlsx
+++ b/E/EG0A.xlsx
@@ -11,29 +11,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="78">
   <si>
     <t/>
   </si>
   <si>
+    <t>20015737</t>
+  </si>
+  <si>
+    <t>IDM NATA DE COCO 900</t>
+  </si>
+  <si>
+    <t>EG0A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20139288</t>
   </si>
   <si>
     <t>LARISST COCOPANDN360</t>
   </si>
   <si>
-    <t>EG0A</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20139289</t>
   </si>
   <si>
@@ -43,13 +52,25 @@
     <t>4</t>
   </si>
   <si>
+    <t>20125696</t>
+  </si>
+  <si>
+    <t>WG.C PUDING MANGO 3S</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20140229</t>
+  </si>
+  <si>
+    <t>W/COCO PUD BLUE3X120</t>
+  </si>
+  <si>
     <t>10004669</t>
   </si>
   <si>
     <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>10004668</t>
@@ -616,14 +637,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -697,10 +718,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
@@ -717,33 +738,33 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -757,30 +778,30 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -788,10 +809,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -800,18 +821,18 @@
         <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -820,18 +841,18 @@
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -840,70 +861,70 @@
         <v>5</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -920,18 +941,18 @@
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -940,18 +961,18 @@
         <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -960,7 +981,7 @@
         <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>6</v>
@@ -968,19 +989,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>6</v>
@@ -988,19 +1009,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
@@ -1008,122 +1029,122 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1137,13 +1158,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1157,32 +1178,92 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="1" t="s">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/E/EG0A.xlsx
+++ b/E/EG0A.xlsx
@@ -136,7 +136,7 @@
     <t>20104000</t>
   </si>
   <si>
-    <t>IDM KACANG ALMOND 65</t>
+    <t>IDM KCG ALMD 65 G</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
@@ -151,7 +151,7 @@
     <t>20022908</t>
   </si>
   <si>
-    <t>S/Q CHUNKY ALMOND 82</t>
+    <t>S/Q CHUNKY ALMD 82 G</t>
   </si>
   <si>
     <t>20096781</t>
